--- a/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2513282_ELIMINGRC12FINAL_PROCESSED.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2513282_ELIMINGRC12FINAL_PROCESSED.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.4307</v>
+        <v>5.928</v>
       </c>
       <c r="E2" t="n">
-        <v>4.3016</v>
+        <v>5.7704</v>
       </c>
       <c r="F2" t="n">
-        <v>0.129</v>
+        <v>0.1575</v>
       </c>
       <c r="G2" t="n">
-        <v>2.2676</v>
+        <v>2.3691</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.8013</v>
+        <v>-0.7091</v>
       </c>
       <c r="I2" t="n">
-        <v>3.0689</v>
+        <v>3.0782</v>
       </c>
       <c r="J2" t="n">
-        <v>3.5341</v>
+        <v>3.8203</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.3073</v>
+        <v>-0.09470000000000001</v>
       </c>
       <c r="L2" t="n">
-        <v>3.8414</v>
+        <v>3.915</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.2665</v>
+        <v>-1.4511</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.494</v>
+        <v>-0.6143999999999999</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.7725</v>
+        <v>-0.8368</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.8002</v>
+        <v>-0.7789</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R2" t="n">
-        <v>1.2003</v>
+        <v>1.1684</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0838</v>
+        <v>1.4072</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1891</v>
+        <v>1.2275</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1053</v>
+        <v>0.1797</v>
       </c>
       <c r="V2" t="n">
-        <v>2.8795</v>
+        <v>2.9305</v>
       </c>
       <c r="W2" t="n">
-        <v>2.579</v>
+        <v>2.67</v>
       </c>
       <c r="X2" t="n">
-        <v>0.3004</v>
+        <v>0.2605</v>
       </c>
     </row>
     <row r="3">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.9074</v>
+        <v>5.2707</v>
       </c>
       <c r="E3" t="n">
-        <v>2.7812</v>
+        <v>4.3808</v>
       </c>
       <c r="F3" t="n">
-        <v>1.1262</v>
+        <v>0.8898</v>
       </c>
       <c r="G3" t="n">
-        <v>1.6698</v>
+        <v>1.771</v>
       </c>
       <c r="H3" t="n">
-        <v>1.3335</v>
+        <v>1.3311</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3363</v>
+        <v>0.4399</v>
       </c>
       <c r="J3" t="n">
-        <v>2.4582</v>
+        <v>2.7629</v>
       </c>
       <c r="K3" t="n">
-        <v>1.485</v>
+        <v>1.6191</v>
       </c>
       <c r="L3" t="n">
-        <v>0.9732</v>
+        <v>1.1437</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.7884</v>
+        <v>-0.9919</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.1515</v>
+        <v>-0.288</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.6369</v>
+        <v>-0.7039</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.6005</v>
+        <v>-1.5579</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.401</v>
+        <v>-3.3105</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8005</v>
+        <v>1.7526</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0186</v>
+        <v>1.1855</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1246</v>
+        <v>1.2653</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.106</v>
+        <v>-0.0799</v>
       </c>
       <c r="V3" t="n">
-        <v>3.8194</v>
+        <v>3.8721</v>
       </c>
       <c r="W3" t="n">
-        <v>3.5993</v>
+        <v>3.6632</v>
       </c>
       <c r="X3" t="n">
-        <v>0.2201</v>
+        <v>0.2089</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. NDOUR</t>
+          <t>V. VINOS ALTEMIR</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.7962</v>
+        <v>3.3345</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1408</v>
+        <v>1.4708</v>
       </c>
       <c r="F4" t="n">
-        <v>2.6554</v>
+        <v>1.8637</v>
       </c>
       <c r="G4" t="n">
-        <v>1.1115</v>
+        <v>4.2836</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9954</v>
+        <v>1.0904</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1162</v>
+        <v>3.1932</v>
       </c>
       <c r="J4" t="n">
-        <v>1.7851</v>
+        <v>2.7979</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2254</v>
+        <v>0.1232</v>
       </c>
       <c r="L4" t="n">
-        <v>1.5598</v>
+        <v>2.6747</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.6736</v>
+        <v>1.4857</v>
       </c>
       <c r="N4" t="n">
-        <v>0.77</v>
+        <v>0.9671999999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.4436</v>
+        <v>0.5185</v>
       </c>
       <c r="P4" t="n">
-        <v>-2.4007</v>
+        <v>-1.3632</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.401</v>
+        <v>-2.3368</v>
       </c>
       <c r="R4" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="S4" t="n">
-        <v>3.7249</v>
+        <v>0.973</v>
       </c>
       <c r="T4" t="n">
-        <v>3.4368</v>
+        <v>1.0097</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2881</v>
+        <v>-0.0367</v>
       </c>
       <c r="V4" t="n">
-        <v>1.3604</v>
+        <v>-0.5590000000000001</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.6802</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>2.0406</v>
+        <v>-0.5590000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>V. VINOS ALTEMIR</t>
+          <t>S. NDOUR</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.7454</v>
+        <v>1.9124</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5991</v>
+        <v>-0.511</v>
       </c>
       <c r="F5" t="n">
-        <v>2.1463</v>
+        <v>2.4234</v>
       </c>
       <c r="G5" t="n">
-        <v>4.35</v>
+        <v>1.0882</v>
       </c>
       <c r="H5" t="n">
-        <v>1.1543</v>
+        <v>1.0155</v>
       </c>
       <c r="I5" t="n">
-        <v>3.1957</v>
+        <v>0.0727</v>
       </c>
       <c r="J5" t="n">
-        <v>2.7596</v>
+        <v>1.9065</v>
       </c>
       <c r="K5" t="n">
-        <v>0.12</v>
+        <v>0.326</v>
       </c>
       <c r="L5" t="n">
-        <v>2.6396</v>
+        <v>1.5805</v>
       </c>
       <c r="M5" t="n">
-        <v>1.5904</v>
+        <v>-0.8183</v>
       </c>
       <c r="N5" t="n">
-        <v>1.0343</v>
+        <v>0.6896</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5561</v>
+        <v>-1.5078</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.4004</v>
+        <v>-2.3368</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.4007</v>
+        <v>-3.3105</v>
       </c>
       <c r="R5" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3154</v>
+        <v>1.8368</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2402</v>
+        <v>1.5551</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0752</v>
+        <v>0.2817</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.5196</v>
+        <v>1.3242</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>-0.6621</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.5196</v>
+        <v>1.9863</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X. ELVIRA GOMEZ</t>
+          <t>V. VINÓS ALTEMIR</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4349</v>
+        <v>1.2158</v>
       </c>
       <c r="E6" t="n">
-        <v>1.263</v>
+        <v>1.2158</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1719</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.6796</v>
+        <v>1.2158</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.4465</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2331</v>
+        <v>1.2158</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.7486</v>
+        <v>1.2158</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.5523</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8037</v>
+        <v>1.2158</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.931</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1058</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.0368</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.2001</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.0003</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.8002</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>5.3948</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.7725</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.6224</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.0803</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.7605</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.3197</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>V. VINÓS ALTEMIR</t>
+          <t>M. DUCH CABEZAS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1998</v>
+        <v>0.3198</v>
       </c>
       <c r="E7" t="n">
-        <v>1.1998</v>
+        <v>-0.1425</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>0.4623</v>
       </c>
       <c r="G7" t="n">
-        <v>1.1998</v>
+        <v>0.5644</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>0.6937</v>
       </c>
       <c r="I7" t="n">
-        <v>1.1998</v>
+        <v>-0.1293</v>
       </c>
       <c r="J7" t="n">
-        <v>1.1998</v>
+        <v>0.0578</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>0.0411</v>
       </c>
       <c r="L7" t="n">
-        <v>1.1998</v>
+        <v>0.0167</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>0.5067</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>-0.146</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-0.1947</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.3895</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>0.1947</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>0.2296</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>0.1892</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>0.0404</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.2795</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. DUCH CABEZAS</t>
+          <t>M. VIEYTES VERDU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5167</v>
+        <v>0.1182</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7548</v>
+        <v>-0.5031</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2381</v>
+        <v>0.6212</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5306</v>
+        <v>-1.9439</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7249</v>
+        <v>-2.3605</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1943</v>
+        <v>0.4166</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.0324</v>
+        <v>-0.6126</v>
       </c>
       <c r="K8" t="n">
-        <v>0.04</v>
+        <v>-2.1449</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.07240000000000001</v>
+        <v>1.5323</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5629999999999999</v>
+        <v>-1.3314</v>
       </c>
       <c r="N8" t="n">
-        <v>0.6849</v>
+        <v>-0.2157</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1219</v>
+        <v>-1.1157</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.2001</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.4001</v>
+        <v>-1.3632</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2001</v>
+        <v>1.3632</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5875</v>
+        <v>1.6253</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3223</v>
+        <v>0.9137</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2652</v>
+        <v>0.7115</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.2598</v>
+        <v>0.4368</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2598</v>
+        <v>-0.1221</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. DOMENGE CABRER</t>
+          <t>X. ELVIRA GOMEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.7481</v>
+        <v>-0.5092</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.7225</v>
+        <v>0.1854</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0257</v>
+        <v>-0.6946</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.7223000000000001</v>
+        <v>-1.7158</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.8579</v>
+        <v>-1.4661</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1356</v>
+        <v>-0.2497</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.658</v>
+        <v>-0.6081</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.658</v>
+        <v>-1.4675</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>0.8594000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.0643</v>
+        <v>-1.1077</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1999</v>
+        <v>0.0014</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1356</v>
+        <v>-1.1091</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-0.1947</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0.9737</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>0.7789</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0258</v>
+        <v>3.4582</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0645</v>
+        <v>2.4808</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0387</v>
+        <v>0.9772999999999999</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-2.0568</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>-0.7137</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.3432</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R. RIU GARCIA</t>
+          <t>J. DOMENGE CABRER</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.9695</v>
+        <v>-0.5857</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.7058</v>
+        <v>-0.6061</v>
       </c>
       <c r="F10" t="n">
-        <v>1.7363</v>
+        <v>0.0204</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.3041</v>
+        <v>-0.7163</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.4952</v>
+        <v>-0.8492</v>
       </c>
       <c r="I10" t="n">
-        <v>1.1911</v>
+        <v>0.1329</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6742</v>
+        <v>-0.644</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.316</v>
+        <v>-0.644</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6418</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0.3701</v>
+        <v>-0.07240000000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1792</v>
+        <v>-0.2053</v>
       </c>
       <c r="O10" t="n">
-        <v>0.5493</v>
+        <v>0.1329</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.0003</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.0006</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.0003</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3349</v>
+        <v>0.1306</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.031</v>
+        <v>0.0378</v>
       </c>
       <c r="U10" t="n">
-        <v>0.366</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. VIEYTES VERDU</t>
+          <t>R. RIU GARCIA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.9886</v>
+        <v>-1.0749</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.9229</v>
+        <v>-2.4166</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9343</v>
+        <v>1.3417</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.8838</v>
+        <v>-0.3308</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.2993</v>
+        <v>-1.5287</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4156</v>
+        <v>1.1979</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.7665999999999999</v>
+        <v>-0.6151</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.2121</v>
+        <v>-1.288</v>
       </c>
       <c r="L11" t="n">
-        <v>1.4455</v>
+        <v>0.6729000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.1171</v>
+        <v>0.2843</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.0872</v>
+        <v>-0.2407</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.0299</v>
+        <v>0.525</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>-0.9737</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.4004</v>
+        <v>-1.9474</v>
       </c>
       <c r="R11" t="n">
-        <v>1.4004</v>
+        <v>0.9737</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4956</v>
+        <v>0.2296</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2755</v>
+        <v>0.1458</v>
       </c>
       <c r="U11" t="n">
-        <v>0.7711</v>
+        <v>0.0837</v>
       </c>
       <c r="V11" t="n">
-        <v>0.3996</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.5196</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.0631</v>
+        <v>-2.0539</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.5881</v>
+        <v>-1.5618</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.475</v>
+        <v>-0.4921</v>
       </c>
       <c r="G12" t="n">
-        <v>0.4599</v>
+        <v>0.4674</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.9848</v>
+        <v>-0.9606</v>
       </c>
       <c r="I12" t="n">
-        <v>1.4447</v>
+        <v>1.4279</v>
       </c>
       <c r="J12" t="n">
-        <v>0.6254</v>
+        <v>0.7265</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.1345</v>
+        <v>-0.0435</v>
       </c>
       <c r="L12" t="n">
-        <v>0.7599</v>
+        <v>0.77</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.1654</v>
+        <v>-0.2591</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.8502999999999999</v>
+        <v>-0.9171</v>
       </c>
       <c r="O12" t="n">
-        <v>0.6849</v>
+        <v>0.6579</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.4007</v>
+        <v>-2.3368</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.0009</v>
+        <v>-2.921</v>
       </c>
       <c r="R12" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="S12" t="n">
-        <v>2.5375</v>
+        <v>1.4898</v>
       </c>
       <c r="T12" t="n">
-        <v>2.4675</v>
+        <v>1.2949</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0699</v>
+        <v>0.195</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.6598</v>
+        <v>-1.6742</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.6802</v>
+        <v>-0.6621</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.9797</v>
+        <v>-1.0121</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>13.2284</v>
+        <v>13.8757</v>
       </c>
       <c r="E13" t="n">
-        <v>4.591399999999999</v>
+        <v>7.282099999999998</v>
       </c>
       <c r="F13" t="n">
-        <v>8.636800000000001</v>
+        <v>6.5933</v>
       </c>
       <c r="G13" t="n">
-        <v>6.9994</v>
+        <v>7.0527</v>
       </c>
       <c r="H13" t="n">
-        <v>-3.6769</v>
+        <v>-3.7435</v>
       </c>
       <c r="I13" t="n">
-        <v>10.6765</v>
+        <v>10.7961</v>
       </c>
       <c r="J13" t="n">
-        <v>9.482399999999998</v>
+        <v>10.8079</v>
       </c>
       <c r="K13" t="n">
-        <v>-4.3098</v>
+        <v>-3.5732</v>
       </c>
       <c r="L13" t="n">
-        <v>13.7923</v>
+        <v>14.381</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.4828</v>
+        <v>-3.7552</v>
       </c>
       <c r="N13" t="n">
-        <v>0.6329000000000001</v>
+        <v>-0.1703</v>
       </c>
       <c r="O13" t="n">
-        <v>-3.1157</v>
+        <v>-3.585</v>
       </c>
       <c r="P13" t="n">
-        <v>-10.003</v>
+        <v>-9.736700000000001</v>
       </c>
       <c r="Q13" t="n">
-        <v>-19.0056</v>
+        <v>-18.5</v>
       </c>
       <c r="R13" t="n">
-        <v>9.002599999999999</v>
+        <v>8.763100000000001</v>
       </c>
       <c r="S13" t="n">
-        <v>12.2922</v>
+        <v>12.5656</v>
       </c>
       <c r="T13" t="n">
-        <v>9.5374</v>
+        <v>10.1198</v>
       </c>
       <c r="U13" t="n">
-        <v>2.754900000000001</v>
+        <v>2.4455</v>
       </c>
       <c r="V13" t="n">
-        <v>3.939400000000001</v>
+        <v>3.9941</v>
       </c>
       <c r="W13" t="n">
-        <v>4.577</v>
+        <v>4.8543</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.6377</v>
+        <v>-0.8602000000000003</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.2795</v>
+        <v>0.7553</v>
       </c>
       <c r="E14" t="n">
-        <v>0.6967</v>
+        <v>-0.4648</v>
       </c>
       <c r="F14" t="n">
-        <v>1.5828</v>
+        <v>1.2201</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.1908</v>
+        <v>-0.2071</v>
       </c>
       <c r="H14" t="n">
-        <v>0.7972</v>
+        <v>0.8437</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.988</v>
+        <v>-1.0507</v>
       </c>
       <c r="J14" t="n">
-        <v>0.6253</v>
+        <v>0.727</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.0946</v>
+        <v>-0.0025</v>
       </c>
       <c r="L14" t="n">
-        <v>0.7199</v>
+        <v>0.7295</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.8162</v>
+        <v>-0.9341</v>
       </c>
       <c r="N14" t="n">
-        <v>0.8918</v>
+        <v>0.8461</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.7079</v>
+        <v>-1.7802</v>
       </c>
       <c r="P14" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.2003</v>
+        <v>-1.1684</v>
       </c>
       <c r="R14" t="n">
-        <v>2.2006</v>
+        <v>2.1421</v>
       </c>
       <c r="S14" t="n">
-        <v>1.7298</v>
+        <v>0.2681</v>
       </c>
       <c r="T14" t="n">
-        <v>1.9519</v>
+        <v>0.6387</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.222</v>
+        <v>-0.3706</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.6802</v>
+        <v>-0.6621</v>
       </c>
       <c r="X14" t="n">
-        <v>0.4204</v>
+        <v>0.3826</v>
       </c>
     </row>
     <row r="15">
@@ -1579,28 +1579,28 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5998</v>
+        <v>0.6158</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5998</v>
+        <v>0.6158</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5998</v>
+        <v>0.6158</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5998</v>
+        <v>0.6158</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5998</v>
+        <v>0.6158</v>
       </c>
       <c r="K15" t="n">
-        <v>0.5998</v>
+        <v>0.6158</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. SALO BLAYA</t>
+          <t>M. BATALLER LOPEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.006</v>
+        <v>0.1631</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4484</v>
+        <v>0.5918</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.4545</v>
+        <v>-0.4286</v>
       </c>
       <c r="G16" t="n">
-        <v>0.52</v>
+        <v>0.4912</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.4955</v>
+        <v>2.1671</v>
       </c>
       <c r="I16" t="n">
-        <v>1.0155</v>
+        <v>-1.6759</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6418</v>
+        <v>1.945</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.638</v>
+        <v>1.2959</v>
       </c>
       <c r="L16" t="n">
-        <v>1.2798</v>
+        <v>0.6491</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.1218</v>
+        <v>-1.4537</v>
       </c>
       <c r="N16" t="n">
-        <v>0.1425</v>
+        <v>0.8712</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2643</v>
+        <v>-2.3249</v>
       </c>
       <c r="P16" t="n">
-        <v>0.4001</v>
+        <v>1.7526</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-0.9737</v>
       </c>
       <c r="R16" t="n">
-        <v>0.4001</v>
+        <v>2.7263</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4066</v>
+        <v>-1.9776</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1934</v>
+        <v>-0.8869</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2132</v>
+        <v>-1.0907</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.5196</v>
+        <v>-0.1032</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.5074</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.5196</v>
+        <v>-0.6105</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. ZHURAVLOV</t>
+          <t>A. SALO BLAYA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3164</v>
+        <v>0.0404</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1182</v>
+        <v>0.4879</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4346</v>
+        <v>-0.4474</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3869</v>
+        <v>0.5221</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7362</v>
+        <v>-0.5024</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3493</v>
+        <v>1.0245</v>
       </c>
       <c r="J17" t="n">
-        <v>1.2672</v>
+        <v>0.6734</v>
       </c>
       <c r="K17" t="n">
-        <v>0.7016</v>
+        <v>-0.6235000000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>0.5656</v>
+        <v>1.2968</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.8803</v>
+        <v>-0.1513</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0346</v>
+        <v>0.1211</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.9149</v>
+        <v>-0.2724</v>
       </c>
       <c r="P17" t="n">
-        <v>1.6005</v>
+        <v>0.3895</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.6005</v>
+        <v>0.3895</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.7038</v>
+        <v>-0.3122</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4688</v>
+        <v>-0.1855</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.235</v>
+        <v>-0.1267</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.5999</v>
+        <v>-0.5590000000000001</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.6802</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.0803</v>
+        <v>-0.5590000000000001</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. KEITA</t>
+          <t>A. MONTAGUT PUNTI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7226</v>
+        <v>-0.2474</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.3664</v>
+        <v>0.5719</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3561</v>
+        <v>-0.8193</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.1779</v>
+        <v>0.02</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.1099</v>
+        <v>0.1934</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.068</v>
+        <v>-0.1734</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.1688</v>
+        <v>1.3159</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.4088</v>
+        <v>0.1078</v>
       </c>
       <c r="L18" t="n">
-        <v>0.24</v>
+        <v>1.2081</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.0091</v>
+        <v>-1.2959</v>
       </c>
       <c r="N18" t="n">
-        <v>0.2989</v>
+        <v>0.0856</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.308</v>
+        <v>-1.3815</v>
       </c>
       <c r="P18" t="n">
-        <v>2.4007</v>
+        <v>0.1947</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-2.1421</v>
       </c>
       <c r="R18" t="n">
-        <v>2.4007</v>
+        <v>2.3368</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.6255</v>
+        <v>-1.0727</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2025</v>
+        <v>-0.1024</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.828</v>
+        <v>-0.9702</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6802</v>
+        <v>0.6105</v>
       </c>
       <c r="W18" t="n">
-        <v>0.5999</v>
+        <v>1.5005</v>
       </c>
       <c r="X18" t="n">
-        <v>0.0803</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. BATALLER LOPEZ</t>
+          <t>D. ZHURAVLOV</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8976</v>
+        <v>-0.282</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0282</v>
+        <v>0.101</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.9258</v>
+        <v>-0.383</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3853</v>
+        <v>0.3703</v>
       </c>
       <c r="H19" t="n">
-        <v>2.0925</v>
+        <v>0.6927</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.7072</v>
+        <v>-0.3224</v>
       </c>
       <c r="J19" t="n">
-        <v>1.6382</v>
+        <v>1.3925</v>
       </c>
       <c r="K19" t="n">
-        <v>1.1087</v>
+        <v>0.7518</v>
       </c>
       <c r="L19" t="n">
-        <v>0.5294</v>
+        <v>0.6407</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.2529</v>
+        <v>-1.0222</v>
       </c>
       <c r="N19" t="n">
-        <v>0.9838</v>
+        <v>-0.0591</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.2366</v>
+        <v>-0.9631</v>
       </c>
       <c r="P19" t="n">
-        <v>1.8005</v>
+        <v>1.5579</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.0003</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.8008</v>
+        <v>1.5579</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.9228</v>
+        <v>-1.5997</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.049</v>
+        <v>-0.6294</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.8738</v>
+        <v>-0.9702</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.1606</v>
+        <v>-0.6105</v>
       </c>
       <c r="W19" t="n">
-        <v>0.4393</v>
+        <v>-0.6621</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.5999</v>
+        <v>0.0516</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>I. JUNCADELLA ENFEDAQUE</t>
+          <t>A. KEITA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.9657</v>
+        <v>-0.3391</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.8942</v>
+        <v>-0.4772</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9285</v>
+        <v>0.1381</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.075</v>
+        <v>-2.1703</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7249</v>
+        <v>-1.0385</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.7999000000000001</v>
+        <v>-1.1318</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.638</v>
+        <v>-1.0139</v>
       </c>
       <c r="K20" t="n">
-        <v>0.04</v>
+        <v>-1.257</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.678</v>
+        <v>0.2432</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5629999999999999</v>
+        <v>-1.1564</v>
       </c>
       <c r="N20" t="n">
-        <v>0.6849</v>
+        <v>0.2185</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1219</v>
+        <v>-1.3749</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.2001</v>
+        <v>2.3368</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.2003</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.0003</v>
+        <v>2.3368</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6907</v>
+        <v>-1.1677</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3156</v>
+        <v>-0.0738</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3751</v>
+        <v>-1.0939</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.6621</v>
       </c>
       <c r="W20" t="n">
-        <v>0.2598</v>
+        <v>0.6105</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.2598</v>
+        <v>0.0516</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. PLANELL IGLESIAS</t>
+          <t>I. JUNCADELLA ENFEDAQUE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.4605</v>
+        <v>-0.7141999999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.4297</v>
+        <v>-1.5133</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0309</v>
+        <v>0.7992</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.7549</v>
+        <v>-0.1168</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.0487</v>
+        <v>0.6937</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.7062</v>
+        <v>-0.8105</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.5962</v>
+        <v>-0.6235000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.6762</v>
+        <v>0.0411</v>
       </c>
       <c r="L21" t="n">
-        <v>0.08</v>
+        <v>-0.6645</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.1587</v>
+        <v>0.5067</v>
       </c>
       <c r="N21" t="n">
-        <v>0.6274999999999999</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.7862</v>
+        <v>-0.146</v>
       </c>
       <c r="P21" t="n">
-        <v>1.0003</v>
+        <v>-0.1947</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.2001</v>
+        <v>-1.1684</v>
       </c>
       <c r="R21" t="n">
-        <v>1.2003</v>
+        <v>0.9737</v>
       </c>
       <c r="S21" t="n">
-        <v>0.174</v>
+        <v>-0.4026</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0468</v>
+        <v>-0.0009</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1272</v>
+        <v>-0.4017</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.88</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.6802</v>
+        <v>0.2795</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.1998</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. MONTAGUT PUNTI</t>
+          <t>A. PLANELL IGLESIAS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.8342</v>
+        <v>-2.0532</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.5187</v>
+        <v>-1.5416</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.3155</v>
+        <v>-0.5115</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0313</v>
+        <v>-0.8052</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2069</v>
+        <v>-0.0626</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1756</v>
+        <v>-0.7426</v>
       </c>
       <c r="J22" t="n">
-        <v>1.1692</v>
+        <v>-0.5501</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0436</v>
+        <v>-0.6311</v>
       </c>
       <c r="L22" t="n">
-        <v>1.1256</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.1379</v>
+        <v>-0.2552</v>
       </c>
       <c r="N22" t="n">
-        <v>0.1633</v>
+        <v>0.5685</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.3011</v>
+        <v>-0.8236</v>
       </c>
       <c r="P22" t="n">
-        <v>0.2001</v>
+        <v>0.9737</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.2006</v>
+        <v>-0.1947</v>
       </c>
       <c r="R22" t="n">
-        <v>2.4007</v>
+        <v>1.1684</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.6654</v>
+        <v>-0.3385</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9468</v>
+        <v>-0.1347</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.7186</v>
+        <v>-0.2037</v>
       </c>
       <c r="V22" t="n">
-        <v>0.5999</v>
+        <v>-1.8832</v>
       </c>
       <c r="W22" t="n">
-        <v>1.4596</v>
+        <v>-0.6621</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.8597</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. CASCALES FERNANDEZ</t>
+          <t>P. MONES RIERA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.1601</v>
+        <v>-2.1947</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.0558</v>
+        <v>-0.9807</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.1043</v>
+        <v>-1.2141</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.3326</v>
+        <v>-1.1942</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.3261</v>
+        <v>-0.0303</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.0066</v>
+        <v>-1.1639</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.618</v>
+        <v>1.5398</v>
       </c>
       <c r="K23" t="n">
-        <v>0.06</v>
+        <v>0.113</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.678</v>
+        <v>1.4268</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.7146</v>
+        <v>-2.734</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.3861</v>
+        <v>-0.1433</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.3286</v>
+        <v>-2.5907</v>
       </c>
       <c r="P23" t="n">
-        <v>0.4001</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-1.9474</v>
       </c>
       <c r="R23" t="n">
-        <v>0.4001</v>
+        <v>2.5316</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9678</v>
+        <v>-1.3052</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4378</v>
+        <v>-0.5731000000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.53</v>
+        <v>-0.7321</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>P. MONES RIERA</t>
+          <t>J. CASCALES FERNANDEZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.2924</v>
+        <v>-3.0451</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.9833</v>
+        <v>-0.9176</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.3092</v>
+        <v>-2.1275</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.1798</v>
+        <v>-2.3924</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.0356</v>
+        <v>-0.3726</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.1442</v>
+        <v>-2.0198</v>
       </c>
       <c r="J24" t="n">
-        <v>1.3508</v>
+        <v>-0.6029</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.0128</v>
+        <v>0.0616</v>
       </c>
       <c r="L24" t="n">
-        <v>1.3636</v>
+        <v>-0.6645</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.5307</v>
+        <v>-1.7894</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.0229</v>
+        <v>-0.4342</v>
       </c>
       <c r="O24" t="n">
-        <v>-2.5078</v>
+        <v>-1.3553</v>
       </c>
       <c r="P24" t="n">
-        <v>0.6002</v>
+        <v>0.3895</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.0006</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.6007</v>
+        <v>0.3895</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.453</v>
+        <v>-0.7628</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.3335</v>
+        <v>-0.3147</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.1194</v>
+        <v>-0.4481</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.452</v>
+        <v>-3.2982</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.2801</v>
+        <v>-3.0666</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.1719</v>
+        <v>-0.2316</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.2116</v>
+        <v>-2.1861</v>
       </c>
       <c r="H25" t="n">
-        <v>0.5355</v>
+        <v>0.5434</v>
       </c>
       <c r="I25" t="n">
-        <v>-2.747</v>
+        <v>-2.7296</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.7885</v>
+        <v>-1.6639</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.3563</v>
+        <v>-0.3027</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.4322</v>
+        <v>-1.3612</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.4231</v>
+        <v>-0.5223</v>
       </c>
       <c r="N25" t="n">
-        <v>0.8918</v>
+        <v>0.8461</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.3149</v>
+        <v>-1.3684</v>
       </c>
       <c r="P25" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.2003</v>
+        <v>-1.1684</v>
       </c>
       <c r="R25" t="n">
-        <v>2.0006</v>
+        <v>1.9474</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.7606000000000001</v>
+        <v>-0.6183</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.211</v>
+        <v>-0.1827</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.5496</v>
+        <v>-0.4356</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.2801</v>
+        <v>-1.2726</v>
       </c>
       <c r="W25" t="n">
-        <v>-0.0803</v>
+        <v>-0.0516</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.1998</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-13.2282</v>
+        <v>-10.5993</v>
       </c>
       <c r="E26" t="n">
-        <v>-8.636900000000001</v>
+        <v>-6.593400000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>-4.5915</v>
+        <v>-4.0056</v>
       </c>
       <c r="G26" t="n">
-        <v>-6.9993</v>
+        <v>-7.0527</v>
       </c>
       <c r="H26" t="n">
-        <v>3.6772</v>
+        <v>3.7434</v>
       </c>
       <c r="I26" t="n">
-        <v>-10.6765</v>
+        <v>-10.7961</v>
       </c>
       <c r="J26" t="n">
-        <v>2.4828</v>
+        <v>3.755100000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.633</v>
+        <v>0.1702000000000001</v>
       </c>
       <c r="L26" t="n">
-        <v>3.1157</v>
+        <v>3.5851</v>
       </c>
       <c r="M26" t="n">
-        <v>-9.4823</v>
+        <v>-10.8078</v>
       </c>
       <c r="N26" t="n">
-        <v>4.3101</v>
+        <v>3.573199999999999</v>
       </c>
       <c r="O26" t="n">
-        <v>-13.7922</v>
+        <v>-14.381</v>
       </c>
       <c r="P26" t="n">
-        <v>10.0029</v>
+        <v>9.736800000000001</v>
       </c>
       <c r="Q26" t="n">
-        <v>-9.0025</v>
+        <v>-8.763100000000001</v>
       </c>
       <c r="R26" t="n">
-        <v>19.0054</v>
+        <v>18.5</v>
       </c>
       <c r="S26" t="n">
-        <v>-12.2924</v>
+        <v>-9.289199999999999</v>
       </c>
       <c r="T26" t="n">
-        <v>-2.7547</v>
+        <v>-2.4454</v>
       </c>
       <c r="U26" t="n">
-        <v>-9.5375</v>
+        <v>-6.843500000000001</v>
       </c>
       <c r="V26" t="n">
-        <v>-3.9395</v>
+        <v>-3.9944</v>
       </c>
       <c r="W26" t="n">
-        <v>0.6376999999999999</v>
+        <v>0.8600000000000001</v>
       </c>
       <c r="X26" t="n">
-        <v>-4.577199999999999</v>
+        <v>-4.8544</v>
       </c>
     </row>
   </sheetData>
